--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,7 +792,7 @@
         <v>126705682</v>
       </c>
       <c r="B3" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,43 +898,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126705504</v>
+        <v>126705656</v>
       </c>
       <c r="B4" t="n">
-        <v>105396</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580750</v>
+        <v>580659</v>
       </c>
       <c r="R4" t="n">
-        <v>6384821</v>
+        <v>6384952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1011,7 @@
         <v>126705508</v>
       </c>
       <c r="B5" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,43 +1118,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126705656</v>
+        <v>126705504</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>105471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580659</v>
+        <v>580750</v>
       </c>
       <c r="R6" t="n">
-        <v>6384952</v>
+        <v>6384821</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,41 +1228,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126705643</v>
+        <v>126705725</v>
       </c>
       <c r="B7" t="n">
-        <v>105396</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
@@ -1271,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580651</v>
+        <v>580643</v>
       </c>
       <c r="R7" t="n">
-        <v>6384923</v>
+        <v>6384949</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1307,6 +1311,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,45 +1343,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126705622</v>
+        <v>126705643</v>
       </c>
       <c r="B8" t="n">
-        <v>91265</v>
+        <v>105471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1557,46 +1563,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126705725</v>
+        <v>126705622</v>
       </c>
       <c r="B10" t="n">
-        <v>98361</v>
+        <v>91339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1604,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580643</v>
+        <v>580651</v>
       </c>
       <c r="R10" t="n">
-        <v>6384949</v>
+        <v>6384923</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,11 +1645,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126705699</v>
+        <v>126705599</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580644</v>
+        <v>580678</v>
       </c>
       <c r="R11" t="n">
-        <v>6384947</v>
+        <v>6384921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126705599</v>
+        <v>126705699</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580678</v>
+        <v>580644</v>
       </c>
       <c r="R12" t="n">
-        <v>6384921</v>
+        <v>6384947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1895,7 @@
         <v>126705775</v>
       </c>
       <c r="B13" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>126705762</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>126705613</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>126705667</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>126705565</v>
       </c>
       <c r="B17" t="n">
-        <v>105396</v>
+        <v>105471</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126705793</v>
+        <v>126705536</v>
       </c>
       <c r="B18" t="n">
-        <v>105396</v>
+        <v>96039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,29 +2453,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2485,10 +2481,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580673</v>
+        <v>580750</v>
       </c>
       <c r="R18" t="n">
-        <v>6384923</v>
+        <v>6384822</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126705536</v>
+        <v>126705793</v>
       </c>
       <c r="B19" t="n">
-        <v>95964</v>
+        <v>105471</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,25 +2555,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580750</v>
+        <v>580673</v>
       </c>
       <c r="R19" t="n">
-        <v>6384822</v>
+        <v>6384923</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2647,6 +2647,565 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>127278521</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>A 34642, Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>580675</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6384724</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>127278552</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>A 34642, Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>580679</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6384721</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>127278624</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 34642, Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>580677</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6384709</v>
+      </c>
+      <c r="S22" t="n">
+        <v>50</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>18 blommor på 5-6 lokaler i sluttningen</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>127278592</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 34642, Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>580669</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6384707</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>127278575</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98436</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 34642, Gölpefall, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>580685</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6384701</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>126705682</v>
       </c>
       <c r="B3" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,43 +898,43 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126705656</v>
+        <v>126705504</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>105477</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580659</v>
+        <v>580750</v>
       </c>
       <c r="R4" t="n">
-        <v>6384952</v>
+        <v>6384821</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126705508</v>
+        <v>126705656</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,12 +1041,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580750</v>
+        <v>580659</v>
       </c>
       <c r="R5" t="n">
-        <v>6384821</v>
+        <v>6384952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,45 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126705504</v>
+        <v>126705508</v>
       </c>
       <c r="B6" t="n">
-        <v>105471</v>
+        <v>98442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1228,46 +1228,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126705725</v>
+        <v>126705858</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>57654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580643</v>
+        <v>580661</v>
       </c>
       <c r="R7" t="n">
-        <v>6384949</v>
+        <v>6384936</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>1 blomma</t>
+          <t>Hörd på avstånd</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1324,7 +1324,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1343,42 +1342,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126705643</v>
+        <v>126705622</v>
       </c>
       <c r="B8" t="n">
-        <v>105471</v>
+        <v>91345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1449,46 +1451,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126705858</v>
+        <v>126705643</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>105477</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1496,13 +1494,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580661</v>
+        <v>580651</v>
       </c>
       <c r="R9" t="n">
-        <v>6384936</v>
+        <v>6384923</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,17 +1532,13 @@
           <t>2025-07-16</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Hörd på avstånd</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1563,45 +1557,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126705622</v>
+        <v>126705725</v>
       </c>
       <c r="B10" t="n">
-        <v>91339</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1609,10 +1604,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580651</v>
+        <v>580643</v>
       </c>
       <c r="R10" t="n">
-        <v>6384923</v>
+        <v>6384949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1645,6 +1640,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,7 +1675,7 @@
         <v>126705599</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126705699</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1895,7 +1895,7 @@
         <v>126705775</v>
       </c>
       <c r="B13" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>126705762</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>126705613</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>126705667</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>126705565</v>
       </c>
       <c r="B17" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>126705536</v>
       </c>
       <c r="B18" t="n">
-        <v>96039</v>
+        <v>96045</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>126705793</v>
       </c>
       <c r="B19" t="n">
-        <v>105471</v>
+        <v>105477</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>127278521</v>
       </c>
       <c r="B20" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
         <v>127278552</v>
       </c>
       <c r="B21" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>127278624</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>127278592</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127278575</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -898,45 +898,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126705504</v>
+        <v>126705508</v>
       </c>
       <c r="B4" t="n">
-        <v>105477</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -1008,43 +1008,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126705656</v>
+        <v>126705504</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>105477</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580659</v>
+        <v>580750</v>
       </c>
       <c r="R5" t="n">
-        <v>6384952</v>
+        <v>6384821</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,7 +1118,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126705508</v>
+        <v>126705656</v>
       </c>
       <c r="B6" t="n">
         <v>98442</v>
@@ -1151,12 +1151,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580750</v>
+        <v>580659</v>
       </c>
       <c r="R6" t="n">
-        <v>6384821</v>
+        <v>6384952</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126705858</v>
+        <v>126705622</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>91345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,21 +1239,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1261,13 +1261,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580661</v>
+        <v>580651</v>
       </c>
       <c r="R7" t="n">
-        <v>6384936</v>
+        <v>6384923</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,17 +1312,13 @@
           <t>2025-07-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hörd på avstånd</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1342,10 +1337,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126705622</v>
+        <v>126705858</v>
       </c>
       <c r="B8" t="n">
-        <v>91345</v>
+        <v>57654</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1353,21 +1348,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1375,12 +1370,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1388,13 +1384,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580651</v>
+        <v>580661</v>
       </c>
       <c r="R8" t="n">
-        <v>6384923</v>
+        <v>6384936</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1426,13 +1422,17 @@
           <t>2025-07-16</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Hörd på avstånd</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126705508</v>
+        <v>126705656</v>
       </c>
       <c r="B4" t="n">
         <v>98442</v>
@@ -931,12 +931,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580750</v>
+        <v>580659</v>
       </c>
       <c r="R4" t="n">
-        <v>6384821</v>
+        <v>6384952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,45 +1008,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126705504</v>
+        <v>126705508</v>
       </c>
       <c r="B5" t="n">
-        <v>105477</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1118,43 +1118,43 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126705656</v>
+        <v>126705504</v>
       </c>
       <c r="B6" t="n">
-        <v>98442</v>
+        <v>105477</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
@@ -1165,10 +1165,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580659</v>
+        <v>580750</v>
       </c>
       <c r="R6" t="n">
-        <v>6384952</v>
+        <v>6384821</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>126705682</v>
       </c>
       <c r="B3" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,10 +898,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126705656</v>
+        <v>126705508</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,12 +931,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580659</v>
+        <v>580750</v>
       </c>
       <c r="R4" t="n">
-        <v>6384952</v>
+        <v>6384821</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,10 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126705508</v>
+        <v>126705656</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,12 +1041,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580750</v>
+        <v>580659</v>
       </c>
       <c r="R5" t="n">
-        <v>6384821</v>
+        <v>6384952</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,7 +1121,7 @@
         <v>126705504</v>
       </c>
       <c r="B6" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
         <v>126705622</v>
       </c>
       <c r="B7" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1451,41 +1451,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126705643</v>
+        <v>126705725</v>
       </c>
       <c r="B9" t="n">
-        <v>105477</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
@@ -1494,10 +1498,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580651</v>
+        <v>580643</v>
       </c>
       <c r="R9" t="n">
-        <v>6384923</v>
+        <v>6384949</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,6 +1534,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1557,45 +1566,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126705725</v>
+        <v>126705643</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>105478</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
@@ -1604,10 +1609,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580643</v>
+        <v>580651</v>
       </c>
       <c r="R10" t="n">
-        <v>6384949</v>
+        <v>6384923</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1640,11 +1645,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1672,10 +1672,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126705599</v>
+        <v>126705699</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580678</v>
+        <v>580644</v>
       </c>
       <c r="R11" t="n">
-        <v>6384921</v>
+        <v>6384947</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126705699</v>
+        <v>126705599</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580644</v>
+        <v>580678</v>
       </c>
       <c r="R12" t="n">
-        <v>6384947</v>
+        <v>6384921</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,7 +1895,7 @@
         <v>126705775</v>
       </c>
       <c r="B13" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2004,7 +2004,7 @@
         <v>126705762</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,7 +2119,7 @@
         <v>126705613</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>126705667</v>
       </c>
       <c r="B16" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>126705565</v>
       </c>
       <c r="B17" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>126705536</v>
       </c>
       <c r="B18" t="n">
-        <v>96045</v>
+        <v>96046</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>126705793</v>
       </c>
       <c r="B19" t="n">
-        <v>105477</v>
+        <v>105478</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2653,7 +2653,7 @@
         <v>127278521</v>
       </c>
       <c r="B20" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127278552</v>
+        <v>127278624</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2807,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580679</v>
+        <v>580677</v>
       </c>
       <c r="R21" t="n">
-        <v>6384721</v>
+        <v>6384709</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,6 +2847,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>18 blommor på 5-6 lokaler i sluttningen</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2863,17 +2872,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127278624</v>
+        <v>127278552</v>
       </c>
       <c r="B22" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,11 +2907,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2921,13 +2926,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580677</v>
+        <v>580679</v>
       </c>
       <c r="R22" t="n">
-        <v>6384709</v>
+        <v>6384721</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2957,11 +2962,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>18 blommor på 5-6 lokaler i sluttningen</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2992,7 +2992,7 @@
         <v>127278592</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3102,7 +3102,7 @@
         <v>127278575</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -1892,56 +1892,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126705775</v>
+        <v>126705762</v>
       </c>
       <c r="B13" t="n">
-        <v>91346</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 34642, Gölpefall, Sm</t>
+          <t>A 34368, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580656</v>
+        <v>580673</v>
       </c>
       <c r="R13" t="n">
-        <v>6384963</v>
+        <v>6384923</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,6 +1975,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,57 +2007,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126705762</v>
+        <v>126705775</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>91346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 34368, Gölpefall, Sm</t>
+          <t>A 34642, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580673</v>
+        <v>580656</v>
       </c>
       <c r="R14" t="n">
-        <v>6384923</v>
+        <v>6384963</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,11 +2089,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -898,7 +898,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126705508</v>
+        <v>126705656</v>
       </c>
       <c r="B4" t="n">
         <v>98443</v>
@@ -931,12 +931,12 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
@@ -945,10 +945,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>580750</v>
+        <v>580659</v>
       </c>
       <c r="R4" t="n">
-        <v>6384821</v>
+        <v>6384952</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1008,43 +1008,43 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126705656</v>
+        <v>126705504</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>105478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -1055,10 +1055,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580659</v>
+        <v>580750</v>
       </c>
       <c r="R5" t="n">
-        <v>6384952</v>
+        <v>6384821</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,45 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126705504</v>
+        <v>126705508</v>
       </c>
       <c r="B6" t="n">
-        <v>105478</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126705622</v>
+        <v>126705858</v>
       </c>
       <c r="B7" t="n">
-        <v>91346</v>
+        <v>57654</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,21 +1239,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1261,12 +1261,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1274,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580651</v>
+        <v>580661</v>
       </c>
       <c r="R7" t="n">
-        <v>6384923</v>
+        <v>6384936</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,13 +1313,17 @@
           <t>2025-07-16</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Hörd på avstånd</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1337,46 +1342,42 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126705858</v>
+        <v>126705643</v>
       </c>
       <c r="B8" t="n">
-        <v>57654</v>
+        <v>105478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>221144</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1384,13 +1385,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580661</v>
+        <v>580651</v>
       </c>
       <c r="R8" t="n">
-        <v>6384936</v>
+        <v>6384923</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,17 +1423,13 @@
           <t>2025-07-16</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Hörd på avstånd</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1566,42 +1563,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126705643</v>
+        <v>126705622</v>
       </c>
       <c r="B10" t="n">
-        <v>105478</v>
+        <v>91346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221144</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>126705699</v>
+        <v>126705599</v>
       </c>
       <c r="B11" t="n">
         <v>98443</v>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580644</v>
+        <v>580678</v>
       </c>
       <c r="R11" t="n">
-        <v>6384947</v>
+        <v>6384921</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>126705599</v>
+        <v>126705699</v>
       </c>
       <c r="B12" t="n">
         <v>98443</v>
@@ -1812,7 +1812,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1829,10 +1829,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580678</v>
+        <v>580644</v>
       </c>
       <c r="R12" t="n">
-        <v>6384921</v>
+        <v>6384947</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126705536</v>
+        <v>126705793</v>
       </c>
       <c r="B18" t="n">
-        <v>96046</v>
+        <v>105478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,25 +2453,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2481,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580750</v>
+        <v>580673</v>
       </c>
       <c r="R18" t="n">
-        <v>6384822</v>
+        <v>6384923</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2544,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126705793</v>
+        <v>126705536</v>
       </c>
       <c r="B19" t="n">
-        <v>105478</v>
+        <v>96046</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2555,29 +2559,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580673</v>
+        <v>580750</v>
       </c>
       <c r="R19" t="n">
-        <v>6384923</v>
+        <v>6384822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2760,7 +2760,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127278624</v>
+        <v>127278552</v>
       </c>
       <c r="B21" t="n">
         <v>98443</v>
@@ -2788,11 +2788,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2811,13 +2807,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580677</v>
+        <v>580679</v>
       </c>
       <c r="R21" t="n">
-        <v>6384709</v>
+        <v>6384721</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2847,11 +2843,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>18 blommor på 5-6 lokaler i sluttningen</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2872,14 +2863,14 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127278552</v>
+        <v>127278624</v>
       </c>
       <c r="B22" t="n">
         <v>98443</v>
@@ -2907,7 +2898,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2926,13 +2921,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580679</v>
+        <v>580677</v>
       </c>
       <c r="R22" t="n">
-        <v>6384721</v>
+        <v>6384709</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2962,6 +2957,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>18 blommor på 5-6 lokaler i sluttningen</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -1228,10 +1228,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126705858</v>
+        <v>126705622</v>
       </c>
       <c r="B7" t="n">
-        <v>57654</v>
+        <v>91346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1239,21 +1239,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1261,13 +1261,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,13 +1274,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580661</v>
+        <v>580651</v>
       </c>
       <c r="R7" t="n">
-        <v>6384936</v>
+        <v>6384923</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1313,17 +1312,13 @@
           <t>2025-07-16</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Hörd på avstånd</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1563,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126705622</v>
+        <v>126705858</v>
       </c>
       <c r="B10" t="n">
-        <v>91346</v>
+        <v>57654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,21 +1569,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1596,12 +1591,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1609,13 +1605,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580651</v>
+        <v>580661</v>
       </c>
       <c r="R10" t="n">
-        <v>6384923</v>
+        <v>6384936</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,13 +1643,17 @@
           <t>2025-07-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hörd på avstånd</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -2653,7 +2653,7 @@
         <v>127278521</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
         <v>127278552</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2873,7 +2873,7 @@
         <v>127278624</v>
       </c>
       <c r="B22" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>127278592</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3102,7 +3102,7 @@
         <v>127278575</v>
       </c>
       <c r="B24" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -2653,7 +2653,7 @@
         <v>127278521</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127278552</v>
+        <v>127278624</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2788,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2807,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580679</v>
+        <v>580677</v>
       </c>
       <c r="R21" t="n">
-        <v>6384721</v>
+        <v>6384709</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,6 +2847,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>18 blommor på 5-6 lokaler i sluttningen</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2870,10 +2879,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127278624</v>
+        <v>127278552</v>
       </c>
       <c r="B22" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2898,11 +2907,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2921,13 +2926,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580677</v>
+        <v>580679</v>
       </c>
       <c r="R22" t="n">
-        <v>6384709</v>
+        <v>6384721</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2957,11 +2962,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>18 blommor på 5-6 lokaler i sluttningen</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,7 +2992,7 @@
         <v>127278592</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127278575</v>
       </c>
       <c r="B24" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -2653,7 +2653,7 @@
         <v>127278521</v>
       </c>
       <c r="B20" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,17 +2753,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127278624</v>
+        <v>127278552</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,11 +2788,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2811,13 +2807,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580677</v>
+        <v>580679</v>
       </c>
       <c r="R21" t="n">
-        <v>6384709</v>
+        <v>6384721</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2847,11 +2843,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>18 blommor på 5-6 lokaler i sluttningen</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2872,17 +2863,17 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127278552</v>
+        <v>127278624</v>
       </c>
       <c r="B22" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,7 +2898,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2926,13 +2921,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580679</v>
+        <v>580677</v>
       </c>
       <c r="R22" t="n">
-        <v>6384721</v>
+        <v>6384709</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2962,6 +2957,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>18 blommor på 5-6 lokaler i sluttningen</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2992,7 +2992,7 @@
         <v>127278592</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3102,7 +3102,7 @@
         <v>127278575</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -2863,7 +2863,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3092,7 +3092,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -2753,14 +2753,14 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127278552</v>
+        <v>127278624</v>
       </c>
       <c r="B21" t="n">
         <v>98450</v>
@@ -2788,7 +2788,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2807,13 +2811,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580679</v>
+        <v>580677</v>
       </c>
       <c r="R21" t="n">
-        <v>6384721</v>
+        <v>6384709</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2843,6 +2847,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>18 blommor på 5-6 lokaler i sluttningen</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2870,7 +2879,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127278624</v>
+        <v>127278552</v>
       </c>
       <c r="B22" t="n">
         <v>98450</v>
@@ -2898,11 +2907,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2921,13 +2926,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580677</v>
+        <v>580679</v>
       </c>
       <c r="R22" t="n">
-        <v>6384709</v>
+        <v>6384721</v>
       </c>
       <c r="S22" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2957,11 +2962,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>18 blommor på 5-6 lokaler i sluttningen</t>
         </is>
       </c>
       <c r="AD22" t="b">

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -2653,7 +2653,7 @@
         <v>127278521</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2760,10 +2760,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127278624</v>
+        <v>127278552</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,11 +2788,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2811,13 +2807,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580677</v>
+        <v>580679</v>
       </c>
       <c r="R21" t="n">
-        <v>6384709</v>
+        <v>6384721</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2847,11 +2843,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-08-05</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>18 blommor på 5-6 lokaler i sluttningen</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2879,10 +2870,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127278552</v>
+        <v>127278624</v>
       </c>
       <c r="B22" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2907,7 +2898,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -2926,13 +2921,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580679</v>
+        <v>580677</v>
       </c>
       <c r="R22" t="n">
-        <v>6384721</v>
+        <v>6384709</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2962,6 +2957,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-05</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>18 blommor på 5-6 lokaler i sluttningen</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,7 +2992,7 @@
         <v>127278592</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127278575</v>
       </c>
       <c r="B24" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -2653,7 +2653,7 @@
         <v>127278521</v>
       </c>
       <c r="B20" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>127278552</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>127278624</v>
       </c>
       <c r="B22" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>127278592</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127278575</v>
       </c>
       <c r="B24" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -2653,7 +2653,7 @@
         <v>127278521</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>127278552</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>127278624</v>
       </c>
       <c r="B22" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>127278592</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127278575</v>
       </c>
       <c r="B24" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -2653,7 +2653,7 @@
         <v>127278521</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2763,7 +2763,7 @@
         <v>127278552</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>127278624</v>
       </c>
       <c r="B22" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>127278592</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127278575</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>126705682</v>
       </c>
       <c r="B3" t="n">
-        <v>91346</v>
+        <v>91339</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126705656</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,45 +1008,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126705504</v>
+        <v>126705508</v>
       </c>
       <c r="B5" t="n">
-        <v>105478</v>
+        <v>98436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1118,45 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126705508</v>
+        <v>126705504</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>105471</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1228,45 +1228,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126705622</v>
+        <v>126705725</v>
       </c>
       <c r="B7" t="n">
-        <v>91346</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1274,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580651</v>
+        <v>580643</v>
       </c>
       <c r="R7" t="n">
-        <v>6384923</v>
+        <v>6384949</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,6 +1311,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,7 +1346,7 @@
         <v>126705643</v>
       </c>
       <c r="B8" t="n">
-        <v>105478</v>
+        <v>105471</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1443,46 +1449,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126705725</v>
+        <v>126705858</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>57654</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1490,13 +1496,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580643</v>
+        <v>580661</v>
       </c>
       <c r="R9" t="n">
-        <v>6384949</v>
+        <v>6384936</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1530,7 +1536,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1 blomma</t>
+          <t>Hörd på avstånd</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1539,7 +1545,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1558,10 +1563,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126705858</v>
+        <v>126705622</v>
       </c>
       <c r="B10" t="n">
-        <v>57654</v>
+        <v>91339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1569,21 +1574,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1591,13 +1596,12 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1605,13 +1609,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580661</v>
+        <v>580651</v>
       </c>
       <c r="R10" t="n">
-        <v>6384936</v>
+        <v>6384923</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1643,17 +1647,13 @@
           <t>2025-07-16</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Hörd på avstånd</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>126705599</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126705699</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,57 +1892,56 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126705762</v>
+        <v>126705775</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>91339</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 34368, Gölpefall, Sm</t>
+          <t>A 34642, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580673</v>
+        <v>580656</v>
       </c>
       <c r="R13" t="n">
-        <v>6384923</v>
+        <v>6384963</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1975,11 +1974,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,56 +2001,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126705775</v>
+        <v>126705762</v>
       </c>
       <c r="B14" t="n">
-        <v>91346</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 34642, Gölpefall, Sm</t>
+          <t>A 34368, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580656</v>
+        <v>580673</v>
       </c>
       <c r="R14" t="n">
-        <v>6384963</v>
+        <v>6384923</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2089,6 +2084,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,7 +2119,7 @@
         <v>126705613</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>126705667</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>126705565</v>
       </c>
       <c r="B17" t="n">
-        <v>105478</v>
+        <v>105471</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126705793</v>
+        <v>126705536</v>
       </c>
       <c r="B18" t="n">
-        <v>105478</v>
+        <v>96039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,29 +2453,25 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2485,10 +2481,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580673</v>
+        <v>580750</v>
       </c>
       <c r="R18" t="n">
-        <v>6384923</v>
+        <v>6384822</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2548,10 +2544,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126705536</v>
+        <v>126705793</v>
       </c>
       <c r="B19" t="n">
-        <v>96046</v>
+        <v>105471</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2559,25 +2555,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580750</v>
+        <v>580673</v>
       </c>
       <c r="R19" t="n">
-        <v>6384822</v>
+        <v>6384923</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
         <v>127278521</v>
       </c>
       <c r="B20" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
+          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
         <v>127278552</v>
       </c>
       <c r="B21" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>127278624</v>
       </c>
       <c r="B22" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>127278592</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127278575</v>
       </c>
       <c r="B24" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>

--- a/artfynd/A 34642-2025 artfynd.xlsx
+++ b/artfynd/A 34642-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>126705682</v>
       </c>
       <c r="B3" t="n">
-        <v>91339</v>
+        <v>91346</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
         <v>126705656</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1008,45 +1008,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126705508</v>
+        <v>126705504</v>
       </c>
       <c r="B5" t="n">
-        <v>98436</v>
+        <v>105478</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1118,45 +1118,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126705504</v>
+        <v>126705508</v>
       </c>
       <c r="B6" t="n">
-        <v>105471</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
@@ -1228,46 +1228,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126705725</v>
+        <v>126705622</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>91346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1275,10 +1274,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580643</v>
+        <v>580651</v>
       </c>
       <c r="R7" t="n">
-        <v>6384949</v>
+        <v>6384923</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,11 +1310,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1346,7 +1340,7 @@
         <v>126705643</v>
       </c>
       <c r="B8" t="n">
-        <v>105471</v>
+        <v>105478</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1449,46 +1443,46 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126705858</v>
+        <v>126705725</v>
       </c>
       <c r="B9" t="n">
-        <v>57654</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1496,13 +1490,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580661</v>
+        <v>580643</v>
       </c>
       <c r="R9" t="n">
-        <v>6384936</v>
+        <v>6384949</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1536,7 +1530,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hörd på avstånd</t>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1545,6 +1539,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1563,10 +1558,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>126705622</v>
+        <v>126705858</v>
       </c>
       <c r="B10" t="n">
-        <v>91339</v>
+        <v>57654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1574,21 +1569,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1596,12 +1591,13 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1609,13 +1605,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580651</v>
+        <v>580661</v>
       </c>
       <c r="R10" t="n">
-        <v>6384923</v>
+        <v>6384936</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1647,13 +1643,17 @@
           <t>2025-07-16</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Hörd på avstånd</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1675,7 +1675,7 @@
         <v>126705599</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>126705699</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1892,56 +1892,57 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126705775</v>
+        <v>126705762</v>
       </c>
       <c r="B13" t="n">
-        <v>91339</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>A 34642, Gölpefall, Sm</t>
+          <t>A 34368, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580656</v>
+        <v>580673</v>
       </c>
       <c r="R13" t="n">
-        <v>6384963</v>
+        <v>6384923</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1974,6 +1975,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-07-16</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2001,57 +2007,56 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126705762</v>
+        <v>126705775</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>91346</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>A 34368, Gölpefall, Sm</t>
+          <t>A 34642, Gölpefall, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580673</v>
+        <v>580656</v>
       </c>
       <c r="R14" t="n">
-        <v>6384923</v>
+        <v>6384963</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2084,11 +2089,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-07-16</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 blomma</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2119,7 +2119,7 @@
         <v>126705613</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>126705667</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>126705565</v>
       </c>
       <c r="B17" t="n">
-        <v>105471</v>
+        <v>105478</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,10 +2442,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126705536</v>
+        <v>126705793</v>
       </c>
       <c r="B18" t="n">
-        <v>96039</v>
+        <v>105478</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2453,25 +2453,29 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2180</v>
+        <v>221144</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -2481,10 +2485,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580750</v>
+        <v>580673</v>
       </c>
       <c r="R18" t="n">
-        <v>6384822</v>
+        <v>6384923</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2544,10 +2548,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126705793</v>
+        <v>126705536</v>
       </c>
       <c r="B19" t="n">
-        <v>105471</v>
+        <v>96046</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2555,29 +2559,25 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221144</v>
+        <v>2180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -2587,10 +2587,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580673</v>
+        <v>580750</v>
       </c>
       <c r="R19" t="n">
-        <v>6384923</v>
+        <v>6384822</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2653,7 +2653,7 @@
         <v>127278521</v>
       </c>
       <c r="B20" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sofia  Kasselstrand , Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sofia  Kasselstrand</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2763,7 +2763,7 @@
         <v>127278552</v>
       </c>
       <c r="B21" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2873,7 +2873,7 @@
         <v>127278624</v>
       </c>
       <c r="B22" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         <v>127278592</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>127278575</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
